--- a/converted_files/837/837I-inst-claim.xlsx
+++ b/converted_files/837/837I-inst-claim.xlsx
@@ -59,7 +59,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:MW3"/>
+  <dimension ref="A1:MZ3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1020,850 +1020,865 @@
       </c>
       <c r="GJ1" s="3" t="inlineStr">
         <is>
+          <t>Treatment1Code</t>
+        </is>
+      </c>
+      <c r="GK1" s="3" t="inlineStr">
+        <is>
+          <t>Treatment2Code</t>
+        </is>
+      </c>
+      <c r="GL1" s="3" t="inlineStr">
+        <is>
+          <t>Treatment3Code</t>
+        </is>
+      </c>
+      <c r="GM1" s="3" t="inlineStr">
+        <is>
           <t>Attachment1ReportTypeCode</t>
         </is>
       </c>
-      <c r="GK1" s="3" t="inlineStr">
+      <c r="GN1" s="3" t="inlineStr">
         <is>
           <t>Attachment1ReportTransmissionCode</t>
         </is>
       </c>
-      <c r="GL1" s="3" t="inlineStr">
+      <c r="GO1" s="3" t="inlineStr">
         <is>
           <t>Attachment1ControlNumber</t>
         </is>
       </c>
-      <c r="GM1" s="3" t="inlineStr">
+      <c r="GP1" s="3" t="inlineStr">
         <is>
           <t>Attachment2ReportTypeCode</t>
         </is>
       </c>
-      <c r="GN1" s="3" t="inlineStr">
+      <c r="GQ1" s="3" t="inlineStr">
         <is>
           <t>Attachment2ReportTransmissionCode</t>
         </is>
       </c>
-      <c r="GO1" s="3" t="inlineStr">
+      <c r="GR1" s="3" t="inlineStr">
         <is>
           <t>Attachment2ControlNumber</t>
         </is>
       </c>
-      <c r="GP1" s="3" t="inlineStr">
+      <c r="GS1" s="3" t="inlineStr">
         <is>
           <t>Attachment3ReportTypeCode</t>
         </is>
       </c>
-      <c r="GQ1" s="3" t="inlineStr">
+      <c r="GT1" s="3" t="inlineStr">
         <is>
           <t>Attachment3ReportTransmissionCode</t>
         </is>
       </c>
-      <c r="GR1" s="3" t="inlineStr">
+      <c r="GU1" s="3" t="inlineStr">
         <is>
           <t>Attachment3ControlNumber</t>
         </is>
       </c>
-      <c r="GS1" s="3" t="inlineStr">
+      <c r="GV1" s="3" t="inlineStr">
         <is>
           <t>AttendingProviderIdentifier</t>
         </is>
       </c>
-      <c r="GT1" s="3" t="inlineStr">
+      <c r="GW1" s="3" t="inlineStr">
         <is>
           <t>AttendingProviderLastNameOrOrgName</t>
         </is>
       </c>
-      <c r="GU1" s="3" t="inlineStr">
+      <c r="GX1" s="3" t="inlineStr">
         <is>
           <t>AttendingProviderFirstName</t>
         </is>
       </c>
-      <c r="GV1" s="3" t="inlineStr">
+      <c r="GY1" s="3" t="inlineStr">
         <is>
           <t>AttendingProviderMiddleName</t>
         </is>
       </c>
-      <c r="GW1" s="3" t="inlineStr">
+      <c r="GZ1" s="3" t="inlineStr">
         <is>
           <t>AttendingProviderProviderTaxonomyCode</t>
         </is>
       </c>
-      <c r="GX1" s="3" t="inlineStr">
+      <c r="HA1" s="3" t="inlineStr">
         <is>
           <t>AttendingProviderAdditionalId1Type</t>
         </is>
       </c>
-      <c r="GY1" s="3" t="inlineStr">
+      <c r="HB1" s="3" t="inlineStr">
         <is>
           <t>AttendingProviderAdditionalId1Identification</t>
         </is>
       </c>
-      <c r="GZ1" s="3" t="inlineStr">
+      <c r="HC1" s="3" t="inlineStr">
         <is>
           <t>AttendingProviderAdditionalId2Type</t>
         </is>
       </c>
-      <c r="HA1" s="3" t="inlineStr">
+      <c r="HD1" s="3" t="inlineStr">
         <is>
           <t>AttendingProviderAdditionalId2Identification</t>
         </is>
       </c>
-      <c r="HB1" s="3" t="inlineStr">
+      <c r="HE1" s="3" t="inlineStr">
         <is>
           <t>OperatingPhysicianIdentifier</t>
         </is>
       </c>
-      <c r="HC1" s="3" t="inlineStr">
+      <c r="HF1" s="3" t="inlineStr">
         <is>
           <t>OperatingPhysicianLastNameOrOrgName</t>
         </is>
       </c>
-      <c r="HD1" s="3" t="inlineStr">
+      <c r="HG1" s="3" t="inlineStr">
         <is>
           <t>OperatingPhysicianFirstName</t>
         </is>
       </c>
-      <c r="HE1" s="3" t="inlineStr">
+      <c r="HH1" s="3" t="inlineStr">
         <is>
           <t>OperatingPhysicianMiddleName</t>
         </is>
       </c>
-      <c r="HF1" s="3" t="inlineStr">
+      <c r="HI1" s="3" t="inlineStr">
         <is>
           <t>OperatingPhysicianAdditionalId1Type</t>
         </is>
       </c>
-      <c r="HG1" s="3" t="inlineStr">
+      <c r="HJ1" s="3" t="inlineStr">
         <is>
           <t>OperatingPhysicianAdditionalId1Identification</t>
         </is>
       </c>
-      <c r="HH1" s="3" t="inlineStr">
+      <c r="HK1" s="3" t="inlineStr">
         <is>
           <t>OperatingPhysicianAdditionalId2Type</t>
         </is>
       </c>
-      <c r="HI1" s="3" t="inlineStr">
+      <c r="HL1" s="3" t="inlineStr">
         <is>
           <t>OperatingPhysicianAdditionalId2Identification</t>
         </is>
       </c>
-      <c r="HJ1" s="3" t="inlineStr">
+      <c r="HM1" s="3" t="inlineStr">
         <is>
           <t>OtherOperatingPhysicianIdentifier</t>
         </is>
       </c>
-      <c r="HK1" s="3" t="inlineStr">
+      <c r="HN1" s="3" t="inlineStr">
         <is>
           <t>OtherOperatingPhysicianLastNameOrOrgName</t>
         </is>
       </c>
-      <c r="HL1" s="3" t="inlineStr">
+      <c r="HO1" s="3" t="inlineStr">
         <is>
           <t>OtherOperatingPhysicianFirstName</t>
         </is>
       </c>
-      <c r="HM1" s="3" t="inlineStr">
+      <c r="HP1" s="3" t="inlineStr">
         <is>
           <t>OtherOperatingPhysicianMiddleName</t>
         </is>
       </c>
-      <c r="HN1" s="3" t="inlineStr">
+      <c r="HQ1" s="3" t="inlineStr">
         <is>
           <t>OtherOperatingPhysicianAdditionalId1Type</t>
         </is>
       </c>
-      <c r="HO1" s="3" t="inlineStr">
+      <c r="HR1" s="3" t="inlineStr">
         <is>
           <t>OtherOperatingPhysicianAdditionalId1Identification</t>
         </is>
       </c>
-      <c r="HP1" s="3" t="inlineStr">
+      <c r="HS1" s="3" t="inlineStr">
         <is>
           <t>OtherOperatingPhysicianAdditionalId2Type</t>
         </is>
       </c>
-      <c r="HQ1" s="3" t="inlineStr">
+      <c r="HT1" s="3" t="inlineStr">
         <is>
           <t>OtherOperatingPhysicianAdditionalId2Identification</t>
         </is>
       </c>
-      <c r="HR1" s="3" t="inlineStr">
+      <c r="HU1" s="3" t="inlineStr">
         <is>
           <t>ReferringProviderIdentifier</t>
         </is>
       </c>
-      <c r="HS1" s="3" t="inlineStr">
+      <c r="HV1" s="3" t="inlineStr">
         <is>
           <t>ReferringProviderLastNameOrOrgName</t>
         </is>
       </c>
-      <c r="HT1" s="3" t="inlineStr">
+      <c r="HW1" s="3" t="inlineStr">
         <is>
           <t>ReferringProviderFirstName</t>
         </is>
       </c>
-      <c r="HU1" s="3" t="inlineStr">
+      <c r="HX1" s="3" t="inlineStr">
         <is>
           <t>ReferringProviderMiddleName</t>
         </is>
       </c>
-      <c r="HV1" s="3" t="inlineStr">
+      <c r="HY1" s="3" t="inlineStr">
         <is>
           <t>ReferringProviderAdditionalId1Type</t>
         </is>
       </c>
-      <c r="HW1" s="3" t="inlineStr">
+      <c r="HZ1" s="3" t="inlineStr">
         <is>
           <t>ReferringProviderAdditionalId1Identification</t>
         </is>
       </c>
-      <c r="HX1" s="3" t="inlineStr">
+      <c r="IA1" s="3" t="inlineStr">
         <is>
           <t>ReferringProviderAdditionalId2Type</t>
         </is>
       </c>
-      <c r="HY1" s="3" t="inlineStr">
+      <c r="IB1" s="3" t="inlineStr">
         <is>
           <t>ReferringProviderAdditionalId2Identification</t>
         </is>
       </c>
-      <c r="HZ1" s="3" t="inlineStr">
+      <c r="IC1" s="3" t="inlineStr">
         <is>
           <t>RenderingProviderIdentifier</t>
         </is>
       </c>
-      <c r="IA1" s="3" t="inlineStr">
+      <c r="ID1" s="3" t="inlineStr">
         <is>
           <t>RenderingProviderLastNameOrOrgName</t>
         </is>
       </c>
-      <c r="IB1" s="3" t="inlineStr">
+      <c r="IE1" s="3" t="inlineStr">
         <is>
           <t>RenderingProviderFirstName</t>
         </is>
       </c>
-      <c r="IC1" s="3" t="inlineStr">
+      <c r="IF1" s="3" t="inlineStr">
         <is>
           <t>RenderingProviderMiddleName</t>
         </is>
       </c>
-      <c r="ID1" s="3" t="inlineStr">
+      <c r="IG1" s="3" t="inlineStr">
         <is>
           <t>RenderingProviderAdditionalId1Type</t>
         </is>
       </c>
-      <c r="IE1" s="3" t="inlineStr">
+      <c r="IH1" s="3" t="inlineStr">
         <is>
           <t>RenderingProviderAdditionalId1Identification</t>
         </is>
       </c>
-      <c r="IF1" s="3" t="inlineStr">
+      <c r="II1" s="3" t="inlineStr">
         <is>
           <t>RenderingProviderAdditionalId2Type</t>
         </is>
       </c>
-      <c r="IG1" s="3" t="inlineStr">
+      <c r="IJ1" s="3" t="inlineStr">
         <is>
           <t>RenderingProviderAdditionalId2Identification</t>
         </is>
       </c>
-      <c r="IH1" s="3" t="inlineStr">
+      <c r="IK1" s="3" t="inlineStr">
         <is>
           <t>ServiceFacilityIdentifier</t>
         </is>
       </c>
-      <c r="II1" s="3" t="inlineStr">
+      <c r="IL1" s="3" t="inlineStr">
         <is>
           <t>ServiceFacilityName</t>
         </is>
       </c>
-      <c r="IJ1" s="3" t="inlineStr">
+      <c r="IM1" s="3" t="inlineStr">
         <is>
           <t>ServiceFacilityAddressLine</t>
         </is>
       </c>
-      <c r="IK1" s="3" t="inlineStr">
+      <c r="IN1" s="3" t="inlineStr">
         <is>
           <t>ServiceFacilityAddressLine2</t>
         </is>
       </c>
-      <c r="IL1" s="3" t="inlineStr">
+      <c r="IO1" s="3" t="inlineStr">
         <is>
           <t>ServiceFacilityAddressCity</t>
         </is>
       </c>
-      <c r="IM1" s="3" t="inlineStr">
+      <c r="IP1" s="3" t="inlineStr">
         <is>
           <t>ServiceFacilityAddressStateCode</t>
         </is>
       </c>
-      <c r="IN1" s="3" t="inlineStr">
+      <c r="IQ1" s="3" t="inlineStr">
         <is>
           <t>ServiceFacilityAddressZipCode</t>
         </is>
       </c>
-      <c r="IO1" s="3" t="inlineStr">
+      <c r="IR1" s="3" t="inlineStr">
         <is>
           <t>ServiceFacilityAdditionalId1Type</t>
         </is>
       </c>
-      <c r="IP1" s="3" t="inlineStr">
+      <c r="IS1" s="3" t="inlineStr">
         <is>
           <t>ServiceFacilityAdditionalId1Identification</t>
         </is>
       </c>
-      <c r="IQ1" s="3" t="inlineStr">
+      <c r="IT1" s="3" t="inlineStr">
         <is>
           <t>ServiceFacilityAdditionalId2Type</t>
         </is>
       </c>
-      <c r="IR1" s="3" t="inlineStr">
+      <c r="IU1" s="3" t="inlineStr">
         <is>
           <t>ServiceFacilityAdditionalId2Identification</t>
         </is>
       </c>
-      <c r="IS1" s="3" t="inlineStr">
+      <c r="IV1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerResponsibilitySequence</t>
         </is>
       </c>
-      <c r="IT1" s="3" t="inlineStr">
+      <c r="IW1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberRelationshipType</t>
         </is>
       </c>
-      <c r="IU1" s="3" t="inlineStr">
+      <c r="IX1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberGroupOrPolicyNumber</t>
         </is>
       </c>
-      <c r="IV1" s="3" t="inlineStr">
+      <c r="IY1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberGroupName</t>
         </is>
       </c>
-      <c r="IW1" s="3" t="inlineStr">
+      <c r="IZ1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberClaimFilingIndicatorCode</t>
         </is>
       </c>
-      <c r="IX1" s="3" t="inlineStr">
+      <c r="JA1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberIdentificationType</t>
         </is>
       </c>
-      <c r="IY1" s="3" t="inlineStr">
+      <c r="JB1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberIdentifier</t>
         </is>
       </c>
-      <c r="IZ1" s="3" t="inlineStr">
+      <c r="JC1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberTaxId</t>
         </is>
       </c>
-      <c r="JA1" s="3" t="inlineStr">
+      <c r="JD1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberLastName</t>
         </is>
       </c>
-      <c r="JB1" s="3" t="inlineStr">
+      <c r="JE1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberFirstName</t>
         </is>
       </c>
-      <c r="JC1" s="3" t="inlineStr">
+      <c r="JF1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberMiddleName</t>
         </is>
       </c>
-      <c r="JD1" s="3" t="inlineStr">
+      <c r="JG1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAddressLine</t>
         </is>
       </c>
-      <c r="JE1" s="3" t="inlineStr">
+      <c r="JH1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAddressLine2</t>
         </is>
       </c>
-      <c r="JF1" s="3" t="inlineStr">
+      <c r="JI1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAddressCity</t>
         </is>
       </c>
-      <c r="JG1" s="3" t="inlineStr">
+      <c r="JJ1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAddressStateCode</t>
         </is>
       </c>
-      <c r="JH1" s="3" t="inlineStr">
+      <c r="JK1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAddressZipCode</t>
         </is>
       </c>
-      <c r="JI1" s="3" t="inlineStr">
+      <c r="JL1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAdjustment1Group</t>
         </is>
       </c>
-      <c r="JJ1" s="3" t="inlineStr">
+      <c r="JM1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAdjustment1ReasonCode</t>
         </is>
       </c>
-      <c r="JK1" s="3" t="inlineStr">
+      <c r="JN1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAdjustment1Amount</t>
         </is>
       </c>
-      <c r="JL1" s="3" t="inlineStr">
+      <c r="JO1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAdjustment1Quantity</t>
         </is>
       </c>
-      <c r="JM1" s="3" t="inlineStr">
+      <c r="JP1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAdjustment2Group</t>
         </is>
       </c>
-      <c r="JN1" s="3" t="inlineStr">
+      <c r="JQ1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAdjustment2ReasonCode</t>
         </is>
       </c>
-      <c r="JO1" s="3" t="inlineStr">
+      <c r="JR1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAdjustment2Amount</t>
         </is>
       </c>
-      <c r="JP1" s="3" t="inlineStr">
+      <c r="JS1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAdjustment2Quantity</t>
         </is>
       </c>
-      <c r="JQ1" s="3" t="inlineStr">
+      <c r="JT1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAdjustment3Group</t>
         </is>
       </c>
-      <c r="JR1" s="3" t="inlineStr">
+      <c r="JU1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAdjustment3ReasonCode</t>
         </is>
       </c>
-      <c r="JS1" s="3" t="inlineStr">
+      <c r="JV1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAdjustment3Amount</t>
         </is>
       </c>
-      <c r="JT1" s="3" t="inlineStr">
+      <c r="JW1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAdjustment3Quantity</t>
         </is>
       </c>
-      <c r="JU1" s="3" t="inlineStr">
+      <c r="JX1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerPaidAmount</t>
         </is>
       </c>
-      <c r="JV1" s="3" t="inlineStr">
+      <c r="JY1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberNonCoveredAmount</t>
         </is>
       </c>
-      <c r="JW1" s="3" t="inlineStr">
+      <c r="JZ1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberRemainingPatientLiabilityAmount</t>
         </is>
       </c>
-      <c r="JX1" s="3" t="inlineStr">
+      <c r="KA1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerClaimControlNumber</t>
         </is>
       </c>
-      <c r="JY1" s="3" t="inlineStr">
+      <c r="KB1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerIdentificationType</t>
         </is>
       </c>
-      <c r="JZ1" s="3" t="inlineStr">
+      <c r="KC1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerIdentifier</t>
         </is>
       </c>
-      <c r="KA1" s="3" t="inlineStr">
+      <c r="KD1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerTaxId</t>
         </is>
       </c>
-      <c r="KB1" s="3" t="inlineStr">
+      <c r="KE1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerName</t>
         </is>
       </c>
-      <c r="KC1" s="3" t="inlineStr">
+      <c r="KF1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerAddressLine</t>
         </is>
       </c>
-      <c r="KD1" s="3" t="inlineStr">
+      <c r="KG1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerAddressLine2</t>
         </is>
       </c>
-      <c r="KE1" s="3" t="inlineStr">
+      <c r="KH1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerAddressCity</t>
         </is>
       </c>
-      <c r="KF1" s="3" t="inlineStr">
+      <c r="KI1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerAddressStateCode</t>
         </is>
       </c>
-      <c r="KG1" s="3" t="inlineStr">
+      <c r="KJ1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerAddressZipCode</t>
         </is>
       </c>
-      <c r="KH1" s="3" t="inlineStr">
+      <c r="KK1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerAdditionalId1Type</t>
         </is>
       </c>
-      <c r="KI1" s="3" t="inlineStr">
+      <c r="KL1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerAdditionalId1Identification</t>
         </is>
       </c>
-      <c r="KJ1" s="3" t="inlineStr">
+      <c r="KM1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerAdditionalId2Type</t>
         </is>
       </c>
-      <c r="KK1" s="3" t="inlineStr">
+      <c r="KN1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerAdditionalId2Identification</t>
         </is>
       </c>
-      <c r="KL1" s="3" t="inlineStr">
+      <c r="KO1" s="3" t="inlineStr">
         <is>
           <t>LineControlNumber</t>
         </is>
       </c>
-      <c r="KM1" s="3" t="inlineStr">
+      <c r="KP1" s="3" t="inlineStr">
         <is>
           <t>LineRevenueCodeCode</t>
         </is>
       </c>
-      <c r="KN1" s="3" t="inlineStr">
+      <c r="KQ1" s="3" t="inlineStr">
         <is>
           <t>LineProcedureCode</t>
         </is>
       </c>
-      <c r="KO1" s="3" t="inlineStr">
+      <c r="KR1" s="3" t="inlineStr">
         <is>
           <t>LineProcedureDescFromClaim</t>
         </is>
       </c>
-      <c r="KP1" s="3" t="inlineStr">
+      <c r="KS1" s="3" t="inlineStr">
         <is>
           <t>LineProcedureModifier1Code</t>
         </is>
       </c>
-      <c r="KQ1" s="3" t="inlineStr">
+      <c r="KT1" s="3" t="inlineStr">
         <is>
           <t>LineProcedureModifier2Code</t>
         </is>
       </c>
-      <c r="KR1" s="3" t="inlineStr">
+      <c r="KU1" s="3" t="inlineStr">
         <is>
           <t>LineProcedureModifier3Code</t>
         </is>
       </c>
-      <c r="KS1" s="3" t="inlineStr">
+      <c r="KV1" s="3" t="inlineStr">
         <is>
           <t>LineProcedureModifier4Code</t>
         </is>
       </c>
-      <c r="KT1" s="3" t="inlineStr">
+      <c r="KW1" s="3" t="inlineStr">
         <is>
           <t>LineChargeAmount</t>
         </is>
       </c>
-      <c r="KU1" s="3" t="inlineStr">
+      <c r="KX1" s="3" t="inlineStr">
         <is>
           <t>LineUnitType</t>
         </is>
       </c>
-      <c r="KV1" s="3" t="inlineStr">
+      <c r="KY1" s="3" t="inlineStr">
         <is>
           <t>LineUnitCount</t>
         </is>
       </c>
-      <c r="KW1" s="3" t="inlineStr">
+      <c r="KZ1" s="3" t="inlineStr">
         <is>
           <t>LineNonCoveredAmount</t>
         </is>
       </c>
-      <c r="KX1" s="3" t="inlineStr">
+      <c r="LA1" s="3" t="inlineStr">
         <is>
           <t>LineServiceDateFrom</t>
         </is>
       </c>
-      <c r="KY1" s="3" t="inlineStr">
+      <c r="LB1" s="3" t="inlineStr">
         <is>
           <t>LineServiceDateTo</t>
         </is>
       </c>
-      <c r="KZ1" s="3" t="inlineStr">
+      <c r="LC1" s="3" t="inlineStr">
         <is>
           <t>LineRepricedReferenceNumber</t>
         </is>
       </c>
-      <c r="LA1" s="3" t="inlineStr">
+      <c r="LD1" s="3" t="inlineStr">
         <is>
           <t>LineAdjustedRepricedReferenceNumber</t>
         </is>
       </c>
-      <c r="LB1" s="3" t="inlineStr">
+      <c r="LE1" s="3" t="inlineStr">
         <is>
           <t>LineServiceTaxAmount</t>
         </is>
       </c>
-      <c r="LC1" s="3" t="inlineStr">
+      <c r="LF1" s="3" t="inlineStr">
         <is>
           <t>LineFacilityTaxAmount</t>
         </is>
       </c>
-      <c r="LD1" s="3" t="inlineStr">
+      <c r="LG1" s="3" t="inlineStr">
         <is>
           <t>LineThirdPartyNote</t>
         </is>
       </c>
-      <c r="LE1" s="3" t="inlineStr">
+      <c r="LH1" s="3" t="inlineStr">
         <is>
           <t>LineDrugCode</t>
         </is>
       </c>
-      <c r="LF1" s="3" t="inlineStr">
+      <c r="LI1" s="3" t="inlineStr">
         <is>
           <t>LineDrugQuantity</t>
         </is>
       </c>
-      <c r="LG1" s="3" t="inlineStr">
+      <c r="LJ1" s="3" t="inlineStr">
         <is>
           <t>LineDrugUnitType</t>
         </is>
       </c>
-      <c r="LH1" s="3" t="inlineStr">
+      <c r="LK1" s="3" t="inlineStr">
         <is>
           <t>LinePrescriptionNumber</t>
         </is>
       </c>
-      <c r="LI1" s="3" t="inlineStr">
+      <c r="LL1" s="3" t="inlineStr">
         <is>
           <t>LineAttachment1ReportTypeCode</t>
         </is>
       </c>
-      <c r="LJ1" s="3" t="inlineStr">
+      <c r="LM1" s="3" t="inlineStr">
         <is>
           <t>LineAttachment1ReportTransmissionCode</t>
         </is>
       </c>
-      <c r="LK1" s="3" t="inlineStr">
+      <c r="LN1" s="3" t="inlineStr">
         <is>
           <t>LineAttachment1ControlNumber</t>
         </is>
       </c>
-      <c r="LL1" s="3" t="inlineStr">
+      <c r="LO1" s="3" t="inlineStr">
         <is>
           <t>LineAttachment2ReportTypeCode</t>
         </is>
       </c>
-      <c r="LM1" s="3" t="inlineStr">
+      <c r="LP1" s="3" t="inlineStr">
         <is>
           <t>LineAttachment2ReportTransmissionCode</t>
         </is>
       </c>
-      <c r="LN1" s="3" t="inlineStr">
+      <c r="LQ1" s="3" t="inlineStr">
         <is>
           <t>LineAttachment2ControlNumber</t>
         </is>
       </c>
-      <c r="LO1" s="3" t="inlineStr">
+      <c r="LR1" s="3" t="inlineStr">
         <is>
           <t>LineAttachment3ReportTypeCode</t>
         </is>
       </c>
-      <c r="LP1" s="3" t="inlineStr">
+      <c r="LS1" s="3" t="inlineStr">
         <is>
           <t>LineAttachment3ReportTransmissionCode</t>
         </is>
       </c>
-      <c r="LQ1" s="3" t="inlineStr">
+      <c r="LT1" s="3" t="inlineStr">
         <is>
           <t>LineAttachment3ControlNumber</t>
         </is>
       </c>
-      <c r="LR1" s="3" t="inlineStr">
+      <c r="LU1" s="3" t="inlineStr">
         <is>
           <t>LineOperatingPhysicianIdentifier</t>
         </is>
       </c>
-      <c r="LS1" s="3" t="inlineStr">
+      <c r="LV1" s="3" t="inlineStr">
         <is>
           <t>LineOperatingPhysicianLastNameOrOrgName</t>
         </is>
       </c>
-      <c r="LT1" s="3" t="inlineStr">
+      <c r="LW1" s="3" t="inlineStr">
         <is>
           <t>LineOperatingPhysicianFirstName</t>
         </is>
       </c>
-      <c r="LU1" s="3" t="inlineStr">
+      <c r="LX1" s="3" t="inlineStr">
         <is>
           <t>LineOperatingPhysicianMiddleName</t>
         </is>
       </c>
-      <c r="LV1" s="3" t="inlineStr">
+      <c r="LY1" s="3" t="inlineStr">
         <is>
           <t>LineOperatingPhysicianAdditionalId1Type</t>
         </is>
       </c>
-      <c r="LW1" s="3" t="inlineStr">
+      <c r="LZ1" s="3" t="inlineStr">
         <is>
           <t>LineOperatingPhysicianAdditionalId1Identification</t>
         </is>
       </c>
-      <c r="LX1" s="3" t="inlineStr">
+      <c r="MA1" s="3" t="inlineStr">
         <is>
           <t>LineOperatingPhysicianAdditionalId2Type</t>
         </is>
       </c>
-      <c r="LY1" s="3" t="inlineStr">
+      <c r="MB1" s="3" t="inlineStr">
         <is>
           <t>LineOperatingPhysicianAdditionalId2Identification</t>
         </is>
       </c>
-      <c r="LZ1" s="3" t="inlineStr">
+      <c r="MC1" s="3" t="inlineStr">
         <is>
           <t>LineOtherOperatingPhysicianIdentifier</t>
         </is>
       </c>
-      <c r="MA1" s="3" t="inlineStr">
+      <c r="MD1" s="3" t="inlineStr">
         <is>
           <t>LineOtherOperatingPhysicianLastNameOrOrgName</t>
         </is>
       </c>
-      <c r="MB1" s="3" t="inlineStr">
+      <c r="ME1" s="3" t="inlineStr">
         <is>
           <t>LineOtherOperatingPhysicianFirstName</t>
         </is>
       </c>
-      <c r="MC1" s="3" t="inlineStr">
+      <c r="MF1" s="3" t="inlineStr">
         <is>
           <t>LineOtherOperatingPhysicianMiddleName</t>
         </is>
       </c>
-      <c r="MD1" s="3" t="inlineStr">
+      <c r="MG1" s="3" t="inlineStr">
         <is>
           <t>LineOtherOperatingPhysicianAdditionalId1Type</t>
         </is>
       </c>
-      <c r="ME1" s="3" t="inlineStr">
+      <c r="MH1" s="3" t="inlineStr">
         <is>
           <t>LineOtherOperatingPhysicianAdditionalId1Identification</t>
         </is>
       </c>
-      <c r="MF1" s="3" t="inlineStr">
+      <c r="MI1" s="3" t="inlineStr">
         <is>
           <t>LineOtherOperatingPhysicianAdditionalId2Type</t>
         </is>
       </c>
-      <c r="MG1" s="3" t="inlineStr">
+      <c r="MJ1" s="3" t="inlineStr">
         <is>
           <t>LineOtherOperatingPhysicianAdditionalId2Identification</t>
         </is>
       </c>
-      <c r="MH1" s="3" t="inlineStr">
+      <c r="MK1" s="3" t="inlineStr">
         <is>
           <t>LineRenderingProviderIdentifier</t>
         </is>
       </c>
-      <c r="MI1" s="3" t="inlineStr">
+      <c r="ML1" s="3" t="inlineStr">
         <is>
           <t>LineRenderingProviderLastNameOrOrgName</t>
         </is>
       </c>
-      <c r="MJ1" s="3" t="inlineStr">
+      <c r="MM1" s="3" t="inlineStr">
         <is>
           <t>LineRenderingProviderFirstName</t>
         </is>
       </c>
-      <c r="MK1" s="3" t="inlineStr">
+      <c r="MN1" s="3" t="inlineStr">
         <is>
           <t>LineRenderingProviderMiddleName</t>
         </is>
       </c>
-      <c r="ML1" s="3" t="inlineStr">
+      <c r="MO1" s="3" t="inlineStr">
         <is>
           <t>LineRenderingProviderAdditionalId1Type</t>
         </is>
       </c>
-      <c r="MM1" s="3" t="inlineStr">
+      <c r="MP1" s="3" t="inlineStr">
         <is>
           <t>LineRenderingProviderAdditionalId1Identification</t>
         </is>
       </c>
-      <c r="MN1" s="3" t="inlineStr">
+      <c r="MQ1" s="3" t="inlineStr">
         <is>
           <t>LineRenderingProviderAdditionalId2Type</t>
         </is>
       </c>
-      <c r="MO1" s="3" t="inlineStr">
+      <c r="MR1" s="3" t="inlineStr">
         <is>
           <t>LineRenderingProviderAdditionalId2Identification</t>
         </is>
       </c>
-      <c r="MP1" s="3" t="inlineStr">
+      <c r="MS1" s="3" t="inlineStr">
         <is>
           <t>LineReferringProviderIdentifier</t>
         </is>
       </c>
-      <c r="MQ1" s="3" t="inlineStr">
+      <c r="MT1" s="3" t="inlineStr">
         <is>
           <t>LineReferringProviderLastNameOrOrgName</t>
         </is>
       </c>
-      <c r="MR1" s="3" t="inlineStr">
+      <c r="MU1" s="3" t="inlineStr">
         <is>
           <t>LineReferringProviderFirstName</t>
         </is>
       </c>
-      <c r="MS1" s="3" t="inlineStr">
+      <c r="MV1" s="3" t="inlineStr">
         <is>
           <t>LineReferringProviderMiddleName</t>
         </is>
       </c>
-      <c r="MT1" s="3" t="inlineStr">
+      <c r="MW1" s="3" t="inlineStr">
         <is>
           <t>LineReferringProviderAdditionalId1Type</t>
         </is>
       </c>
-      <c r="MU1" s="3" t="inlineStr">
+      <c r="MX1" s="3" t="inlineStr">
         <is>
           <t>LineReferringProviderAdditionalId1Identification</t>
         </is>
       </c>
-      <c r="MV1" s="3" t="inlineStr">
+      <c r="MY1" s="3" t="inlineStr">
         <is>
           <t>LineReferringProviderAdditionalId2Type</t>
         </is>
       </c>
-      <c r="MW1" s="3" t="inlineStr">
+      <c r="MZ1" s="3" t="inlineStr">
         <is>
           <t>LineReferringProviderAdditionalId2Identification</t>
         </is>
@@ -1872,7 +1887,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6497613a0e499095d1</t>
+          <t>6aaaca96b439338235b48eeb</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2294,40 +2309,40 @@
       <c r="GP2"/>
       <c r="GQ2"/>
       <c r="GR2"/>
-      <c r="GS2" s="3" t="inlineStr">
+      <c r="GS2"/>
+      <c r="GT2"/>
+      <c r="GU2"/>
+      <c r="GV2" s="3" t="inlineStr">
         <is>
           <t>1122334455</t>
         </is>
       </c>
-      <c r="GT2" s="3" t="inlineStr">
+      <c r="GW2" s="3" t="inlineStr">
         <is>
           <t>JONES</t>
         </is>
       </c>
-      <c r="GU2" s="3" t="inlineStr">
+      <c r="GX2" s="3" t="inlineStr">
         <is>
           <t>JOHN</t>
         </is>
       </c>
-      <c r="GV2" s="3" t="inlineStr">
+      <c r="GY2" s="3" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="GW2"/>
-      <c r="GX2" s="3" t="inlineStr">
+      <c r="GZ2"/>
+      <c r="HA2" s="3" t="inlineStr">
         <is>
           <t>PROVIDER_UPIN_NUMBER</t>
         </is>
       </c>
-      <c r="GY2" s="3" t="inlineStr">
+      <c r="HB2" s="3" t="inlineStr">
         <is>
           <t>B99937</t>
         </is>
       </c>
-      <c r="GZ2"/>
-      <c r="HA2"/>
-      <c r="HB2"/>
       <c r="HC2"/>
       <c r="HD2"/>
       <c r="HE2"/>
@@ -2370,81 +2385,81 @@
       <c r="IP2"/>
       <c r="IQ2"/>
       <c r="IR2"/>
-      <c r="IS2" s="3" t="inlineStr">
+      <c r="IS2"/>
+      <c r="IT2"/>
+      <c r="IU2"/>
+      <c r="IV2" s="3" t="inlineStr">
         <is>
           <t>SECONDARY</t>
         </is>
       </c>
-      <c r="IT2" s="3" t="inlineStr">
+      <c r="IW2" s="3" t="inlineStr">
         <is>
           <t>SPOUSE</t>
         </is>
       </c>
-      <c r="IU2" s="3" t="inlineStr">
+      <c r="IX2" s="3" t="inlineStr">
         <is>
           <t>351630</t>
         </is>
       </c>
-      <c r="IV2" s="3" t="inlineStr">
+      <c r="IY2" s="3" t="inlineStr">
         <is>
           <t>STATE TEACHERS</t>
         </is>
       </c>
-      <c r="IW2" s="3" t="inlineStr">
+      <c r="IZ2" s="3" t="inlineStr">
         <is>
           <t>CI</t>
         </is>
       </c>
-      <c r="IX2" s="3" t="inlineStr">
+      <c r="JA2" s="3" t="inlineStr">
         <is>
           <t>MEMBER_ID</t>
         </is>
       </c>
-      <c r="IY2" s="3" t="inlineStr">
+      <c r="JB2" s="3" t="inlineStr">
         <is>
           <t>222004433</t>
         </is>
       </c>
-      <c r="IZ2"/>
-      <c r="JA2" s="3" t="inlineStr">
+      <c r="JC2"/>
+      <c r="JD2" s="3" t="inlineStr">
         <is>
           <t>DOE</t>
         </is>
       </c>
-      <c r="JB2" s="3" t="inlineStr">
+      <c r="JE2" s="3" t="inlineStr">
         <is>
           <t>JANE</t>
         </is>
       </c>
-      <c r="JC2" s="3" t="inlineStr">
+      <c r="JF2" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="JD2" s="3" t="inlineStr">
+      <c r="JG2" s="3" t="inlineStr">
         <is>
           <t>125 CITY AVENUE</t>
         </is>
       </c>
-      <c r="JE2"/>
-      <c r="JF2" s="3" t="inlineStr">
+      <c r="JH2"/>
+      <c r="JI2" s="3" t="inlineStr">
         <is>
           <t>CENTERVILLE</t>
         </is>
       </c>
-      <c r="JG2" s="3" t="inlineStr">
+      <c r="JJ2" s="3" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="JH2" s="3" t="inlineStr">
+      <c r="JK2" s="3" t="inlineStr">
         <is>
           <t>17111</t>
         </is>
       </c>
-      <c r="JI2"/>
-      <c r="JJ2"/>
-      <c r="JK2"/>
       <c r="JL2"/>
       <c r="JM2"/>
       <c r="JN2"/>
@@ -2458,72 +2473,72 @@
       <c r="JV2"/>
       <c r="JW2"/>
       <c r="JX2"/>
-      <c r="JY2" s="3" t="inlineStr">
-        <is>
-          <t>PAYOR_ID</t>
-        </is>
-      </c>
-      <c r="JZ2" s="3" t="inlineStr">
-        <is>
-          <t>1135</t>
-        </is>
-      </c>
+      <c r="JY2"/>
+      <c r="JZ2"/>
       <c r="KA2"/>
       <c r="KB2" s="3" t="inlineStr">
         <is>
+          <t>PAYOR_ID</t>
+        </is>
+      </c>
+      <c r="KC2" s="3" t="inlineStr">
+        <is>
+          <t>1135</t>
+        </is>
+      </c>
+      <c r="KD2"/>
+      <c r="KE2" s="3" t="inlineStr">
+        <is>
           <t>STATE TEACHERS</t>
         </is>
       </c>
-      <c r="KC2"/>
-      <c r="KD2"/>
-      <c r="KE2"/>
       <c r="KF2"/>
       <c r="KG2"/>
       <c r="KH2"/>
       <c r="KI2"/>
       <c r="KJ2"/>
       <c r="KK2"/>
-      <c r="KL2" s="3" t="inlineStr">
+      <c r="KL2"/>
+      <c r="KM2"/>
+      <c r="KN2"/>
+      <c r="KO2" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="KM2" s="3" t="inlineStr">
+      <c r="KP2" s="3" t="inlineStr">
         <is>
           <t>0305</t>
         </is>
       </c>
-      <c r="KN2" s="3" t="inlineStr">
+      <c r="KQ2" s="3" t="inlineStr">
         <is>
           <t>85025</t>
         </is>
       </c>
-      <c r="KO2"/>
-      <c r="KP2"/>
-      <c r="KQ2"/>
       <c r="KR2"/>
       <c r="KS2"/>
-      <c r="KT2" s="1" t="n">
+      <c r="KT2"/>
+      <c r="KU2"/>
+      <c r="KV2"/>
+      <c r="KW2" s="1" t="n">
         <v>13.39</v>
       </c>
-      <c r="KU2" s="3" t="inlineStr">
+      <c r="KX2" s="3" t="inlineStr">
         <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="KV2" t="n">
+      <c r="KY2" t="n">
         <v>1.0</v>
       </c>
-      <c r="KW2"/>
-      <c r="KX2" s="4" t="n">
+      <c r="KZ2"/>
+      <c r="LA2" s="4" t="n">
         <v>42624.0</v>
       </c>
-      <c r="KY2" s="4" t="n">
+      <c r="LB2" s="4" t="n">
         <v>42624.0</v>
       </c>
-      <c r="KZ2"/>
-      <c r="LA2"/>
-      <c r="LB2"/>
       <c r="LC2"/>
       <c r="LD2"/>
       <c r="LE2"/>
@@ -2571,11 +2586,14 @@
       <c r="MU2"/>
       <c r="MV2"/>
       <c r="MW2"/>
+      <c r="MX2"/>
+      <c r="MY2"/>
+      <c r="MZ2"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6497613a0e499095d1</t>
+          <t>6aaaca96b439338235b48eeb</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2878,47 +2896,47 @@
       <c r="KI3"/>
       <c r="KJ3"/>
       <c r="KK3"/>
-      <c r="KL3" s="3" t="inlineStr">
+      <c r="KL3"/>
+      <c r="KM3"/>
+      <c r="KN3"/>
+      <c r="KO3" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="KM3" s="3" t="inlineStr">
+      <c r="KP3" s="3" t="inlineStr">
         <is>
           <t>0730</t>
         </is>
       </c>
-      <c r="KN3" s="3" t="inlineStr">
+      <c r="KQ3" s="3" t="inlineStr">
         <is>
           <t>93005</t>
         </is>
       </c>
-      <c r="KO3"/>
-      <c r="KP3"/>
-      <c r="KQ3"/>
       <c r="KR3"/>
       <c r="KS3"/>
-      <c r="KT3" s="1" t="n">
+      <c r="KT3"/>
+      <c r="KU3"/>
+      <c r="KV3"/>
+      <c r="KW3" s="1" t="n">
         <v>76.54</v>
       </c>
-      <c r="KU3" s="3" t="inlineStr">
+      <c r="KX3" s="3" t="inlineStr">
         <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="KV3" t="n">
+      <c r="KY3" t="n">
         <v>3.0</v>
       </c>
-      <c r="KW3"/>
-      <c r="KX3" s="4" t="n">
+      <c r="KZ3"/>
+      <c r="LA3" s="4" t="n">
         <v>42624.0</v>
       </c>
-      <c r="KY3" s="4" t="n">
+      <c r="LB3" s="4" t="n">
         <v>42624.0</v>
       </c>
-      <c r="KZ3"/>
-      <c r="LA3"/>
-      <c r="LB3"/>
       <c r="LC3"/>
       <c r="LD3"/>
       <c r="LE3"/>
@@ -2966,6 +2984,9 @@
       <c r="MU3"/>
       <c r="MV3"/>
       <c r="MW3"/>
+      <c r="MX3"/>
+      <c r="MY3"/>
+      <c r="MZ3"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
